--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0169.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0169.xlsx
@@ -18193,7 +18193,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Đừng lo, {PlayerName}, việc này đơn giản lắm. Bình thường thì tớ sẽ để cậu tự cậu mò, nhưng bà Linghan mất tích rồi, không thể chậm trễ được. Để tớ hướng dẫn cậu nhé.</t>
+          <t>Đừng lo, {PlayerName}, việc này đơn giản lắm. Bình thường thì tớ sẽ để cậu tự mày mò, nhưng bà Linghan mất tích rồi, không thể chậm trễ được. Để tớ hướng dẫn cậu nhé.</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Nhiều năm trước, đúng vào ngày này, Kim Châu đã bị bao vây bởi một đợt bùng phát Tacet Discord dữ dội. Hàng chục Midnight Rangers đã kiên cường đứng vững trên tiền tuyến, đối mặt với hàng ngàn Tacet Discord.</t>
+          <t>Nhiều năm trước, đúng vào ngày này, Jinzhou đã bị bao vây bởi một đợt bùng phát Tacet Discord dữ dội. Hàng chục Midnight Rangers đã kiên cường đứng vững trên tiền tuyến, đối mặt với hàng ngàn Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Đáng ra đây phải là suy nghĩ trong đầu ta chứ!</t>
+          <t>Đáng ra đây phải là suy nghĩ trong đầu tao chứ!</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Ít nhất khi ta tìm ra thằng khách hàng vô trách nhiệm đó, ta sẽ nói chuyện cứng rắn hơn và ĐÒI LẠI SỐ TIỀN Ta XỨNG ĐÁNG!</t>
+          <t>Ít nhất khi tao tìm ra thằng khách hàng vô trách nhiệm đó, tao sẽ nói chuyện cứng rắn hơn và ĐÒI LẠI SỐ TIỀN TAO XỨNG ĐÁNG!</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sáng nay ta ăn Rainbow Bean Pop Rock, rồi thì...</t>
+          <t>Sáng nay tao ăn Rainbow Bean Pop Rock, rồi thì...</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Cô ấy nhíu cậu, rõ ràng đang rất khó khăn để thích nghi với sự thay đổi.</t>
+          <t>Cô ấy nhíu mày, rõ ràng đang rất khó khăn để thích nghi với sự thay đổi.</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi. Ta thừa nhận. Ta không ăn kẹo đâu.</t>
+          <t>Được rồi, được rồi. Tao thừa nhận. Tao không ăn kẹo đâu.</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Và tôi xin đảm bảo, tôi không phải là người gây ra sự bất thường này đâu. Tôi hứa với cậu điều đó.</t>
+          <t>Và tôi xin đảm bảo, tôi không phải là người gây ra sự bất thường này đâu. Tôi hứa với bạn điều đó.</t>
         </is>
       </c>
     </row>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Ừm, ta nghĩ cậu đang tiến rất gần đến câu trả lời mình tìm kiếm rồi đấy.</t>
+          <t>Ừm, tao nghĩ cậu đang tiến rất gần đến câu trả lời mình tìm kiếm rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Gần đó, Denia đứng khoanh tay, nở nụ cười khó chịu kiểu "Ta biết hết nhưng không thèm nói".</t>
+          <t>Gần đó, Denia đứng khoanh tay, nở nụ cười khó chịu kiểu "Tao biết hết nhưng không thèm nói".</t>
         </is>
       </c>
     </row>
@@ -22613,7 +22613,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Luuk nhíu cậu, một nỗi sợ hãi bất chợt ập đến.</t>
+          <t>Luuk nhíu mày, một nỗi sợ hãi bất chợt ập đến.</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hôm nay ta đang hào phóng, hắn mới may mắn đấy.</t>
+          <t>Hôm nay tao đang hào phóng, hắn mới may mắn đấy.</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Để ta nói thẳng cho rõ. (Dù sao ta cũng sẽ nói thật.) Hiệu ứng của viên kẹo này nghiêm trọng lắm đấy... (Và ta biết cậu sẽ không dễ dãi với ta đâu.)</t>
+          <t>Để tao nói thẳng cho rõ. (Dù sao tao cũng sẽ nói thật.) Hiệu ứng của viên kẹo này nghiêm trọng lắm đấy... (Và tao biết cậu sẽ không dễ dãi với tao đâu.)</t>
         </is>
       </c>
     </row>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Cậu có ăn kẹo đó không?</t>
+          <t>Cậu đã ăn cái kẹo đó chưa?</t>
         </is>
       </c>
     </row>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>...Tớ có.</t>
+          <t>...Tôi đã làm rồi.</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Câu trả lời của cô khiến cậu nhíu cậu.</t>
+          <t>Câu trả lời của cô khiến cậu nhíu mày.</t>
         </is>
       </c>
     </row>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Kim Châu, Hẻm núi Chuông Vang, Làng Kỳ Xí, Tàn tích Tòa án Savantae... cậu nhớ lại từng ký ức về những nơi mình đã đi qua.</t>
+          <t>Jinzhou, Hẻm núi Chuông Vang, Làng Kỳ Xí, Tàn tích Tòa án Savantae... cậu nhớ lại từng ký ức về những nơi mình đã đi qua.</t>
         </is>
       </c>
     </row>
@@ -28138,7 +28138,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Gì?</t>
         </is>
       </c>
     </row>
